--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="网页原文" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Java常用单词" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Python常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FastAPI常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LangChain常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Python补充" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FastAPI补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="LangChain与RAG补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Transformer补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="OpenCV补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="AI编程工具补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Java后端补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="说明" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J318"/>
+  <dimension ref="A1:J319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17648,6 +17648,58 @@
       <c r="J318" s="2" t="inlineStr">
         <is>
           <t>做登录鉴权和权限控制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>阿-普-呃-勒</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>/ˈæp.əl/</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>一句话：一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J319"/>
+  <dimension ref="A1:J320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17700,6 +17700,54 @@
       <c r="J319" t="inlineStr">
         <is>
           <t>一句话：一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -17724,7 +17724,6 @@
           <t>普-伊-恩-克</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>pink</t>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J320"/>
+  <dimension ref="A1:J321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17747,6 +17747,58 @@
       <c r="J320" t="inlineStr">
         <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>布-勒-克</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>/blak/</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>blackball / blacklist / blacken</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J321"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17799,6 +17799,54 @@
       <c r="J321" t="inlineStr">
         <is>
           <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>伊-斯</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -17823,7 +17823,6 @@
           <t>伊-斯</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
           <t>IS</t>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J322"/>
+  <dimension ref="A1:J323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17846,6 +17846,58 @@
       <c r="J322" t="inlineStr">
         <is>
           <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>添加的行为或实例。</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>阿-德</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>/æd/</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>coalesce / join / unite</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>一句话：添加的行为或实例。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J323"/>
+  <dimension ref="A1:J324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17898,6 +17898,54 @@
       <c r="J323" t="inlineStr">
         <is>
           <t>一句话：添加的行为或实例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>idemmode</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>伊-德-诶-姆-姆-德-诶</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>idemmode</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J324"/>
+  <dimension ref="A1:J325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17922,7 +17922,6 @@
           <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>idemmode</t>
@@ -17946,6 +17945,54 @@
       <c r="J324" t="inlineStr">
         <is>
           <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>德-诶-勒-诶-特-诶</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -17969,7 +17969,6 @@
           <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>delete</t>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1100,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J325"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17992,6 +17992,54 @@
       <c r="J325" t="inlineStr">
         <is>
           <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>德-诶-勒</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="网页原文" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Java常用单词" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FastAPI常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="LangChain常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Python补充" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="FastAPI补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="LangChain与RAG补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Transformer补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="OpenCV补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="AI编程工具补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Java后端补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="说明" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18016,7 +18017,6 @@
           <t>德-诶-勒</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
           <t>del</t>
@@ -18049,6 +18049,1956 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>单词</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>用法/解释</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>中文谐音</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>音标</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>发音</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>技术栈</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>重要程度</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>对比词</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>一句话回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>检索增强生成：先查资料再生成</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>拉格</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>/ræg/</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>rag</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>微调 / 纯 Prompt</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>用外部知识降低幻觉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>chunking</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>文本分块，便于嵌入和检索</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>畅-金</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>/ˈtʃʌŋkɪŋ/</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>chunk-ing</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>整篇塞上下文</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>把长文档切成可检索片段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>chunk overlap</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>分块重叠，减少跨段信息丢失</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>畅克-欧-弗-莱普</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>/tʃʌŋk ˈəʊvəlæp/</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>chunk oh-ver-lap</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>无重叠硬切</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>相邻块共享一段边界文本。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>RecursiveCharacterTextSplitter</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>按字符递归切分的常用分块器</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>瑞-克-瑟-西-弗-凯-瑞-克特-斯普利特</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>/rɪˈkɜːsɪv ˈkærəktə tekst ˈsplɪtə/</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ri-kur-siv character text splitter</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>TokenTextSplitter</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>按分隔符优先级递归切块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TokenTextSplitter</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>按 token 数切分文本</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>托-肯-泰克斯特-斯普利特</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>/ˈtəʊkən tekst ˈsplɪtə/</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>token text splitter</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>字符切分</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>更贴近模型上下文计量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>embedding model</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>把文本变成向量的模型</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>艾姆-贝-丁-莫-德</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>/ɪmˈbedɪŋ ˈmɒdl/</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>im-bed-ing model</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>生成模型 LLM</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>用于语义检索，不是直接写答案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>vector database</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>向量数据库，存向量并近邻搜索</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>维克特-戴-塔-贝斯</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>/ˈvektə ˈdeɪtəbeɪs/</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>vec-ter day-ta-base</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>关系库 LIKE 查询</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>按相似度找回相关片段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FAISS</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Facebook 开源向量检索库</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>菲斯</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>/faɪs/</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>fice</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Chroma / Milvus</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>本地快速做向量近邻搜索。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Chroma</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>轻量向量库，开发友好</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>克-罗-玛</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>/ˈkrəʊmə/</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>kro-muh</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>FAISS / pgvector</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>快速搭建本地知识库。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Milvus</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>面向生产的向量数据库</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>米尔-弗斯</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>/ˈmɪlvəs/</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mil-vus</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>FAISS</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>大规模向量检索可选用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>pgvector</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PostgreSQL 向量扩展</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>皮-吉-维克特</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>/ˌpiː dʒiː ˈvektə/</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>P-G vector</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>专用向量库</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>业务库和向量库一体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>similarity search</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>相似度搜索</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>西-米-拉-瑞-提-瑟奇</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>/ˌsɪməˈlærəti sɜːtʃ/</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>sim-i-la-ri-tee search</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>关键词搜索</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>按向量距离找最相近文档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>hybrid search</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>混合检索：关键词+向量</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>海-布瑞德-瑟奇</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>/ˈhaɪbrɪd sɜːtʃ/</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>hi-brid search</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>纯向量检索</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>专名靠词，语义靠向量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>BM25</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>经典关键词相关性算法</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>比-艾姆-吐-五</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>/ˌbiː em twenti ˈfaɪv/</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>B-M twenty-five</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>TF-IDF / 向量检索</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>稀疏检索常用打分函数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>rerank</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>对召回结果重排序</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>瑞-兰克</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>/ˌriːˈræŋk/</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ree-rank</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>只靠向量 Top-K</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>用更准模型精排候选片段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Top-K</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>取相似度最高的 K 条</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>托普-凯</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>/tɒp keɪ/</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>top kay</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>阈值过滤</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>控制送进 Prompt 的片段数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>metadata filtering</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>按元数据过滤检索结果</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>梅-塔-戴-塔-菲-欧-特-林</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>/ˈmetədeɪtə ˈfɪltərɪŋ/</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>meta-data filtering</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>纯相似度</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>按来源/时间/类目缩小范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>答案引用检索来源</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>赛-泰-申</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>/saɪˈteɪʃən/</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>sigh-tay-shun</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>无引用生成</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>可追溯，降低瞎编。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>幻觉：编造不实内容</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>哈-卢-西-内-申</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>/həˌluːsɪˈneɪʃən/</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>huh-loo-si-nay-shun</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>拒答 / 检索约束</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>RAG 和人审就是为压它。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>LCEL</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>LangChain 表达式语言，管道组合组件</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>艾欧西伊艾欧</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>/ˌel siː iː ˈel/</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>L-C-E-L</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>老版 Chain 类</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>用 | 把 prompt、模型、解析串起来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PromptTemplate</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>提示词模板</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>普-罗姆普特-坦普雷特</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>/prɒmpt ˈtemplət/</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>prompt tem-plit</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>硬编码字符串</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>把变量填进固定提示结构。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ChatPromptTemplate</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>多角色聊天提示模板</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>恰特-普-罗姆普特-坦普雷特</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>/tʃæt prɒmpt ˈtemplət/</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>chat prompt tem-plit</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>PromptTemplate</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>组装 system/user/assistant 消息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>OutputParser</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>把模型输出解析成结构化数据</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>奥特-普特-帕-瑟</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>/ˈaʊtpʊt ˈpɑːsə/</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>out-put par-ser</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>手工正则抠文本</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>稳定提取 JSON/对象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>tool calling</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>工具调用，模型决定调哪个函数</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>图-欧-考-林</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>/tuːl ˈkɔːlɪŋ/</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>tool call-ing</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>纯文本回答</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>让模型联动检索、计算、API。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LangChain</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>对话记忆，保存历史上下文</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>梅-莫-瑞</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>/ˈmeməri/</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>mem-uh-ree</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>无状态单轮</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>支持多轮连续对话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>StateGraph</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>状态图，LangGraph 编排核心</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>斯忒特-格-拉夫</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>/steɪt ɡrɑːf/</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>state graph</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>线性 Chain</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>用节点和边描述复杂流程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>检查点，持久化图状态</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>切克-波因特</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>/ˈtʃekpɔɪnt/</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>check-point</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>无状态重跑</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>支持暂停恢复和排错回放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>interrupt</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>中断，人在回路时挂起</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>因-特-拉普特</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>/ˌɪntəˈrʌpt/</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>in-tuh-rupt</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>全自动执行</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>关键步骤等人审再继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>human-in-the-loop</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>人在回路，人工确认关键步骤</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>休-曼-因-泽-鲁普</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>/ˈhjuːmən ɪn ðə luːp/</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>human in the loop</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>全自动 Agent</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>高风险操作必须人审。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LangGraph</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>conditional edge</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>条件边，按状态路由下一节点</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康-迪-申-纳-欧-艾奇</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>/kənˈdɪʃənl edʒ/</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>kun-dish-uh-nul edge</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>固定顺序边</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>实现分支和重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Ollama</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>本地运行开源大模型的工具</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>欧-拉-玛</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>/əˈlɑːmə/</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>uh-lah-muh</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>云端 API</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>本机一键 pull/run 模型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI API</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 兼容的大模型接口</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>欧-潘-诶-诶皮艾</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>/ˈəʊpən eɪ aɪ ˈeɪ piː aɪ/</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>open AI A-P-I</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>本地推理</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>用 HTTP 调云端对话/嵌入模型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>温度，控制输出随机性</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>坦-普-拉-切</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>/ˈtemprətʃə/</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>tem-pruh-chur</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>top_p</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>越高越发散，越低越稳。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>top_p</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>核采样，按概率质量截断</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>托普-皮</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>/tɒp piː/</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>top pee</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>另一种控制多样性的参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>max_tokens</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>最大生成 token 数</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>麦克斯-托-肯斯</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>/mæks ˈtəʊkənz/</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>max tokens</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>上下文窗口</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>限制回答长度和费用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>streaming</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>流式输出，边生成边返回</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>斯-特-瑞-明</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>/ˈstriːmɪŋ/</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>stream-ing</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>一次性返回</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>降低首字等待，体验更好。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19426,7 +21376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20388,7 +22338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21038,7 +22988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23144,7 +25094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23463,6 +25413,468 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>单词</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>用法/解释</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>中文谐音</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>音标</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>发音</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>技术栈</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>重要程度</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>对比词</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>一句话回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>添加的行为或实例。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>阿-德</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>/æd/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>coalesce / join / unite</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>一句话：添加的行为或实例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>阿-普-呃-勒</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/ˈæp.əl/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>一句话：一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>布-勒-克</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/blak/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>blackball / blacklist / blacken</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>德-诶-勒</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>德-诶-勒-诶-特-诶</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>idemmode</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>伊-德-诶-姆-姆-德-诶</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>idemmode</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>伊-斯</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27388,7 +29800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29442,7 +31854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31340,7 +33752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33030,7 +35442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35708,7 +38120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36722,7 +39134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37838,1954 +40250,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>单词</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>用法/解释</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>中文谐音</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>音标</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>发音</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>技术栈</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>重要程度</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>对比词</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>一句话回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>检索增强生成：先查资料再生成</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>拉格</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>/ræg/</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>rag</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>微调 / 纯 Prompt</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>用外部知识降低幻觉。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>chunking</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>文本分块，便于嵌入和检索</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>畅-金</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>/ˈtʃʌŋkɪŋ/</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>chunk-ing</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>整篇塞上下文</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>把长文档切成可检索片段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>chunk overlap</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>分块重叠，减少跨段信息丢失</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>畅克-欧-弗-莱普</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>/tʃʌŋk ˈəʊvəlæp/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>chunk oh-ver-lap</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>无重叠硬切</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>相邻块共享一段边界文本。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>RecursiveCharacterTextSplitter</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>按字符递归切分的常用分块器</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>瑞-克-瑟-西-弗-凯-瑞-克特-斯普利特</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>/rɪˈkɜːsɪv ˈkærəktə tekst ˈsplɪtə/</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>ri-kur-siv character text splitter</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>TokenTextSplitter</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>按分隔符优先级递归切块。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>TokenTextSplitter</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>按 token 数切分文本</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>托-肯-泰克斯特-斯普利特</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>/ˈtəʊkən tekst ˈsplɪtə/</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>token text splitter</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>字符切分</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>更贴近模型上下文计量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>embedding model</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>把文本变成向量的模型</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>艾姆-贝-丁-莫-德</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>/ɪmˈbedɪŋ ˈmɒdl/</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>im-bed-ing model</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>生成模型 LLM</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>用于语义检索，不是直接写答案。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>vector database</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>向量数据库，存向量并近邻搜索</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>维克特-戴-塔-贝斯</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>/ˈvektə ˈdeɪtəbeɪs/</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>vec-ter day-ta-base</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>关系库 LIKE 查询</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>按相似度找回相关片段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>FAISS</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Facebook 开源向量检索库</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>菲斯</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>/faɪs/</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>fice</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Chroma / Milvus</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>本地快速做向量近邻搜索。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Chroma</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>轻量向量库，开发友好</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>克-罗-玛</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>/ˈkrəʊmə/</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>kro-muh</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>FAISS / pgvector</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>快速搭建本地知识库。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Milvus</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>面向生产的向量数据库</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>米尔-弗斯</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>/ˈmɪlvəs/</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>mil-vus</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>FAISS</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>大规模向量检索可选用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>pgvector</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>PostgreSQL 向量扩展</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>皮-吉-维克特</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>/ˌpiː dʒiː ˈvektə/</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>P-G vector</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>专用向量库</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>业务库和向量库一体。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>similarity search</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>相似度搜索</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>西-米-拉-瑞-提-瑟奇</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>/ˌsɪməˈlærəti sɜːtʃ/</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>sim-i-la-ri-tee search</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>关键词搜索</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>按向量距离找最相近文档。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>hybrid search</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>混合检索：关键词+向量</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>海-布瑞德-瑟奇</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>/ˈhaɪbrɪd sɜːtʃ/</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>hi-brid search</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>纯向量检索</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>专名靠词，语义靠向量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>BM25</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>经典关键词相关性算法</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>比-艾姆-吐-五</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>/ˌbiː em twenti ˈfaɪv/</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>B-M twenty-five</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>TF-IDF / 向量检索</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>稀疏检索常用打分函数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>rerank</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>对召回结果重排序</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>瑞-兰克</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>/ˌriːˈræŋk/</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ree-rank</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>只靠向量 Top-K</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>用更准模型精排候选片段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Top-K</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>取相似度最高的 K 条</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>托普-凯</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>/tɒp keɪ/</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>top kay</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>阈值过滤</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>控制送进 Prompt 的片段数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>metadata filtering</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>按元数据过滤检索结果</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>梅-塔-戴-塔-菲-欧-特-林</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>/ˈmetədeɪtə ˈfɪltərɪŋ/</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>meta-data filtering</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>纯相似度</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>按来源/时间/类目缩小范围。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>答案引用检索来源</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>赛-泰-申</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>/saɪˈteɪʃən/</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>sigh-tay-shun</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>无引用生成</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>可追溯，降低瞎编。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>hallucination</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>幻觉：编造不实内容</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>哈-卢-西-内-申</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>/həˌluːsɪˈneɪʃən/</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>huh-loo-si-nay-shun</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>拒答 / 检索约束</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>RAG 和人审就是为压它。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>LCEL</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>LangChain 表达式语言，管道组合组件</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>艾欧西伊艾欧</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>/ˌel siː iː ˈel/</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>L-C-E-L</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>老版 Chain 类</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>用 | 把 prompt、模型、解析串起来。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>PromptTemplate</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>提示词模板</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>普-罗姆普特-坦普雷特</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>/prɒmpt ˈtemplət/</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>prompt tem-plit</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>硬编码字符串</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>把变量填进固定提示结构。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>ChatPromptTemplate</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>多角色聊天提示模板</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>恰特-普-罗姆普特-坦普雷特</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>/tʃæt prɒmpt ˈtemplət/</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>chat prompt tem-plit</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>PromptTemplate</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>组装 system/user/assistant 消息。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>OutputParser</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>把模型输出解析成结构化数据</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>奥特-普特-帕-瑟</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>/ˈaʊtpʊt ˈpɑːsə/</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>out-put par-ser</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>手工正则抠文本</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>稳定提取 JSON/对象。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>tool calling</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>工具调用，模型决定调哪个函数</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>图-欧-考-林</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>/tuːl ˈkɔːlɪŋ/</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>tool call-ing</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>纯文本回答</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>让模型联动检索、计算、API。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>对话记忆，保存历史上下文</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>梅-莫-瑞</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>/ˈmeməri/</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>mem-uh-ree</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>无状态单轮</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>支持多轮连续对话。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>StateGraph</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>状态图，LangGraph 编排核心</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>斯忒特-格-拉夫</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>/steɪt ɡrɑːf/</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>state graph</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>线性 Chain</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>用节点和边描述复杂流程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>checkpoint</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>检查点，持久化图状态</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>切克-波因特</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>/ˈtʃekpɔɪnt/</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>check-point</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>无状态重跑</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>支持暂停恢复和排错回放。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>interrupt</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>中断，人在回路时挂起</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>因-特-拉普特</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>/ˌɪntəˈrʌpt/</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>in-tuh-rupt</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>全自动执行</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>关键步骤等人审再继续。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>human-in-the-loop</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>人在回路，人工确认关键步骤</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>休-曼-因-泽-鲁普</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>/ˈhjuːmən ɪn ðə luːp/</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>human in the loop</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>全自动 Agent</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>高风险操作必须人审。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>conditional edge</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>条件边，按状态路由下一节点</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>康-迪-申-纳-欧-艾奇</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>/kənˈdɪʃənl edʒ/</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>kun-dish-uh-nul edge</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>固定顺序边</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>实现分支和重试。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>模型</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Ollama</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>本地运行开源大模型的工具</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>欧-拉-玛</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>/əˈlɑːmə/</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>uh-lah-muh</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>云端 API</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>本机一键 pull/run 模型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>模型</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI API</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>OpenAI 兼容的大模型接口</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>欧-潘-诶-诶皮艾</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>/ˈəʊpən eɪ aɪ ˈeɪ piː aɪ/</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>open AI A-P-I</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>本地推理</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>用 HTTP 调云端对话/嵌入模型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>模型</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>温度，控制输出随机性</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>坦-普-拉-切</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>/ˈtemprətʃə/</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>tem-pruh-chur</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>top_p</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>越高越发散，越低越稳。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>模型</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>top_p</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>核采样，按概率质量截断</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>托普-皮</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>/tɒp piː/</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>top pee</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>另一种控制多样性的参数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>模型</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>max_tokens</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>最大生成 token 数</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>麦克斯-托-肯斯</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>/mæks ˈtəʊkənz/</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>max tokens</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>常问</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>上下文窗口</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>限制回答长度和费用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>模型</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>streaming</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>流式输出，边生成边返回</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>斯-特-瑞-明</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>/ˈstriːmɪŋ/</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>stream-ing</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>一次性返回</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>降低首字等待，体验更好。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="说明" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J326"/>
+  <dimension ref="A1:J327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18040,6 +18040,54 @@
       <c r="J326" t="inlineStr">
         <is>
           <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>弗-尔</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25418,7 +25466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25733,23 +25781,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25769,7 +25817,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25781,23 +25829,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -25817,7 +25865,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25829,41 +25877,89 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J327"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18064,7 +18064,6 @@
           <t>弗-尔</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>for</t>
@@ -18088,6 +18087,54 @@
       <c r="J327" t="inlineStr">
         <is>
           <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>future</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>弗-乌-特-乌-尔-诶</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>future</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25466,7 +25513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25829,23 +25876,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -25865,7 +25912,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25877,23 +25924,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -25913,7 +25960,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25925,41 +25972,89 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18111,7 +18111,6 @@
           <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>future</t>
@@ -18135,6 +18134,54 @@
       <c r="J328" t="inlineStr">
         <is>
           <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>better：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>布-诶-特-特-诶-尔</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>一句话：better：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25513,7 +25560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25680,27 +25727,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>better</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>better：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>布-勒-克</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>/blak/</t>
-        </is>
-      </c>
+          <t>布-诶-特-特-诶-尔</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>better</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -25715,12 +25758,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>blackball / blacklist / blacken</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>一句话：better：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25732,23 +25775,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>布-勒-克</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/blak/</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>black</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -25763,12 +25810,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>blackball / blacklist / blacken</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
     </row>
@@ -25780,23 +25827,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>德-诶-勒</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -25816,7 +25863,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25828,23 +25875,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25864,7 +25911,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25876,23 +25923,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -25912,7 +25959,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25924,23 +25971,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -25960,7 +26007,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25972,23 +26019,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -26008,7 +26055,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26020,41 +26067,89 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J329"/>
+  <dimension ref="A1:J330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18158,7 +18158,6 @@
           <t>布-诶-特-特-诶-尔</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>better</t>
@@ -18182,6 +18181,54 @@
       <c r="J329" t="inlineStr">
         <is>
           <t>一句话：better：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26152,6 +26199,54 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="说明" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18205,7 +18205,6 @@
           <t>斯-特-尔-乌-格-格-勒-诶</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
           <t>struggle</t>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="说明" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J330"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18228,6 +18228,54 @@
       <c r="J330" t="inlineStr">
         <is>
           <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>布-勒-诶-恩</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -25606,7 +25654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25868,28 +25916,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>未分类</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
+          <t>布-勒-诶-恩</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -25909,7 +25957,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -25921,23 +25969,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>德-诶-勒</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25957,7 +26005,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25969,23 +26017,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -26005,7 +26053,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26017,23 +26065,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -26053,7 +26101,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26065,23 +26113,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -26101,7 +26149,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26113,23 +26161,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26149,7 +26197,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26161,23 +26209,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -26197,7 +26245,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26209,41 +26257,89 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>struggle</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J331"/>
+  <dimension ref="A1:J332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18252,7 +18252,6 @@
           <t>布-勒-诶-恩</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
           <t>boolean</t>
@@ -18276,6 +18275,54 @@
       <c r="J331" t="inlineStr">
         <is>
           <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>斯-特-阿-特-伊-克</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26300,46 +26347,94 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
+          <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>struggle</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J332"/>
+  <dimension ref="A1:J333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18299,7 +18299,6 @@
           <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
           <t>static</t>
@@ -18323,6 +18322,50 @@
       <c r="J332" t="inlineStr">
         <is>
           <t>能说明 static 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>super</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>super：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>斯-乌-普-伊-尔</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>能说明 super 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -25701,7 +25744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26437,6 +26480,50 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>super</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>super：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>斯-乌-普-伊-尔</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>能说明 super 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J333"/>
+  <dimension ref="A1:J334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18346,8 +18346,6 @@
           <t>斯-乌-普-伊-尔</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>通用</t>
@@ -18366,6 +18364,58 @@
       <c r="J333" t="inlineStr">
         <is>
           <t>能说明 super 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Blue：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>布-勒-乌-伊</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>/blʌe/</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>/blʌe/</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>能说明 Blue 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -25744,7 +25794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26006,28 +26056,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>Blue：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>布-勒-诶-恩</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>布-勒-乌-伊</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>/blʌe/</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>/blʌe/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -26047,35 +26101,35 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
+          <t>能说明 Blue 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>未分类</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
+          <t>布-勒-诶-恩</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -26095,7 +26149,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -26107,23 +26161,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>德-诶-勒</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -26143,7 +26197,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26155,23 +26209,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -26191,7 +26245,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26203,23 +26257,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -26239,7 +26293,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26251,23 +26305,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26287,7 +26341,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26299,23 +26353,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -26335,7 +26389,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26347,23 +26401,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -26383,35 +26437,35 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>斯-特-阿-特-伊-克</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -26431,35 +26485,35 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
+          <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -26479,49 +26533,97 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>社区·未分类</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>super</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>super：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>斯-乌-普-伊-尔</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>能说明 super 的含义，并举例它在项目中的用法。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J334"/>
+  <dimension ref="A1:J335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18416,6 +18416,54 @@
       <c r="J334" t="inlineStr">
         <is>
           <t>能说明 Blue 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>adminopen</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>adminopen：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>德-姆-伊-恩-普-诶-恩</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>adminopen</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>一句话：adminopen：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25909,27 +25957,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>adminopen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
+          <t>adminopen：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>阿-普-呃-勒</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>/ˈæp.əl/</t>
-        </is>
-      </c>
+          <t>德-姆-伊-恩-普-诶-恩</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>adminopen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -25949,7 +25993,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>一句话：一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
+          <t>一句话：adminopen：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -25961,23 +26005,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>better：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>布-诶-特-特-诶-尔</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>阿-普-呃-勒</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/ˈæp.əl/</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -25997,7 +26045,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>一句话：better：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：一种常见的圆形果实，由Malus domestica树生产，在温和的气候下种植。</t>
         </is>
       </c>
     </row>
@@ -26009,27 +26057,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>better</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>better：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>布-勒-克</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>/blak/</t>
-        </is>
-      </c>
+          <t>布-诶-特-特-诶-尔</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>better</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -26044,44 +26088,44 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>blackball / blacklist / blacken</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>一句话：better：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blue：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>布-勒-乌-伊</t>
+          <t>布-勒-克</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>/blʌe/</t>
+          <t>/blak/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/blʌe/</t>
+          <t>black</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -26096,40 +26140,44 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>blackball / blacklist / blacken</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>能说明 Blue 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>Blue：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>布-勒-诶-恩</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>布-勒-乌-伊</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>/blʌe/</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>/blʌe/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -26149,35 +26197,35 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
+          <t>能说明 Blue 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>未分类</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
+          <t>布-勒-诶-恩</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -26197,7 +26245,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -26209,23 +26257,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>德-诶-勒</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>del</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -26245,7 +26293,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26257,23 +26305,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -26293,7 +26341,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26305,23 +26353,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26341,7 +26389,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26353,23 +26401,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -26389,7 +26437,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26401,23 +26449,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -26437,7 +26485,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -26449,23 +26497,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -26485,35 +26533,35 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>斯-特-阿-特-伊-克</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -26533,35 +26581,35 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
+          <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -26581,49 +26629,97 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>社区·未分类</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>super</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>super：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>斯-乌-普-伊-尔</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>能说明 super 的含义，并举例它在项目中的用法。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -18440,7 +18440,6 @@
           <t>德-姆-伊-恩-普-诶-恩</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>adminopen</t>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J335"/>
+  <dimension ref="A1:J336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18463,6 +18463,58 @@
       <c r="J335" t="inlineStr">
         <is>
           <t>一句话：adminopen：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>社区·RAG · AI</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>革命社会主义者或（最常见的）共产主义者； （通常大写）布尔什维克，俄国内战中布尔什维克的支持者。</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>诶-德</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>/ɹɛd/</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>/ɹɛd/</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>blood / brick / cardinal</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>革命社会主义者或（最常见的）共产主义者。</t>
         </is>
       </c>
     </row>
@@ -25841,7 +25893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26587,33 +26639,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区·RAG · AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>革命社会主义者或（最常见的）共产主义者； （通常大写）布尔什维克，俄国内战中布尔什维克的支持者。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>斯-特-阿-特-伊-克</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>诶-德</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>/ɹɛd/</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>/ɹɛd/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -26623,40 +26679,40 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>blood / brick / cardinal</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
+          <t>革命社会主义者或（最常见的）共产主义者。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
+          <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>struggle</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -26676,49 +26732,97 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>struggle</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>社区·未分类</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>super</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>super：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>斯-乌-普-伊-尔</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>能说明 super 的含义，并举例它在项目中的用法。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI分类-目录" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI分类-全部词汇" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python-FastAPI" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM-RAG-LangChain" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer-OpenCV" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docker-K8s" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI工具开发" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构通用" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="说明" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="AI分类-目录" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="AI分类-全部词汇" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Python-FastAPI" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="LLM-RAG-LangChain" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Transformer-OpenCV" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Docker-K8s" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="AI工具开发" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Java后端" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="架构通用" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1906,7 +1906,6 @@
           <t>德-姆-伊-恩-普-诶-恩</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>adminopen</t>
@@ -4034,7 +4033,6 @@
           <t>布-诶-特-特-诶-尔</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>better</t>
@@ -4498,7 +4496,6 @@
           <t>布-勒-诶-恩</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>boolean</t>
@@ -8290,7 +8287,6 @@
           <t>德-诶-勒</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>del</t>
@@ -8338,7 +8334,6 @@
           <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>delete</t>
@@ -10882,7 +10877,6 @@
           <t>弗-尔</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>for</t>
@@ -11034,7 +11028,6 @@
           <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>future</t>
@@ -12954,7 +12947,6 @@
           <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>idemmode</t>
@@ -13782,7 +13774,6 @@
           <t>伊-斯</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>IS</t>
@@ -18978,7 +18969,6 @@
           <t>普-伊-恩-克</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>pink</t>
@@ -25266,7 +25256,6 @@
           <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
-      <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr">
         <is>
           <t>static</t>
@@ -25574,7 +25563,6 @@
           <t>斯-特-尔-乌-格-格-勒-诶</t>
         </is>
       </c>
-      <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr">
         <is>
           <t>struggle</t>
@@ -25674,8 +25662,6 @@
           <t>斯-乌-普-伊-尔</t>
         </is>
       </c>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
           <t>通用</t>
@@ -37160,7 +37146,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -37405,7 +37390,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
@@ -38213,7 +38197,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
@@ -59221,6 +59204,7 @@
           <t>德-姆-伊-恩-普-诶-恩</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>adminopen</t>
@@ -59320,6 +59304,7 @@
           <t>布-诶-特-特-诶-尔</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>better</t>
@@ -59471,6 +59456,7 @@
           <t>布-勒-诶-恩</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>boolean</t>
@@ -59518,6 +59504,7 @@
           <t>德-诶-勒</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>del</t>
@@ -59565,6 +59552,7 @@
           <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>delete</t>
@@ -59612,6 +59600,7 @@
           <t>弗-尔</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>for</t>
@@ -59659,6 +59648,7 @@
           <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>future</t>
@@ -59706,6 +59696,7 @@
           <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>idemmode</t>
@@ -59753,6 +59744,7 @@
           <t>伊-斯</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>IS</t>
@@ -59800,6 +59792,7 @@
           <t>普-伊-恩-克</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>pink</t>
@@ -59899,6 +59892,7 @@
           <t>斯-特-阿-特-伊-克</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>static</t>
@@ -59946,6 +59940,7 @@
           <t>斯-特-尔-乌-格-格-勒-诶</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>struggle</t>
@@ -59993,6 +59988,8 @@
           <t>斯-乌-普-伊-尔</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>通用</t>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -59076,7 +59076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59186,7 +59186,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -59196,18 +59196,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>adminopen：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>adminopen：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>德-姆-伊-恩-普-诶-恩</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>阿-德-姆-伊-恩-欧-普-伊-恩</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/ædmɪnɒpen/</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>adminopen</t>
+          <t>/ædmɪnɒpen/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -59227,7 +59231,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>一句话：adminopen：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 adminopen 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59386,32 +59390,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>未分类</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Blue：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>布-勒-乌-伊</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>/blʌe/</t>
-        </is>
-      </c>
+          <t>布-勒-诶-恩</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/blʌe/</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59431,35 +59431,35 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>能说明 Blue 的含义，并举例它在项目中的用法。</t>
+          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>布-勒-诶-恩</t>
+          <t>德-诶-勒</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>del</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59479,7 +59479,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59491,23 +59491,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59527,7 +59527,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59539,23 +59539,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -59575,7 +59575,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59587,23 +59587,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -59623,7 +59623,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59635,23 +59635,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -59671,7 +59671,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59683,23 +59683,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -59719,7 +59719,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59731,23 +59731,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -59767,7 +59767,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59779,23 +59779,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>struggle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>斯-特-尔-乌-格-格-勒-诶</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>struggle</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -59815,199 +59815,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>社区·RAG · AI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>革命社会主义者或（最常见的）共产主义者； （通常大写）布尔什维克，俄国内战中布尔什维克的支持者。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>诶-德</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>/ɹɛd/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>/ɹɛd/</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>blood / brick / cardinal</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>革命社会主义者或（最常见的）共产主义者。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>社区·未分类</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>static</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>static：面试中需能解释其含义，并结合项目说明使用场景。</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>斯-特-阿-特-伊-克</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>static</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>能说明 static 的含义，并举例它在项目中的用法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>struggle</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>struggle</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
           <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>社区·未分类</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>super</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>super：面试中需能解释其含义，并结合项目说明使用场景。</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>斯-乌-普-伊-尔</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>能说明 super 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -59076,7 +59076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59390,28 +59390,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>boolean：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>布-勒-诶-恩</t>
+          <t>德-诶-勒</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>del</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59431,7 +59431,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>能说明 boolean 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59443,23 +59443,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59479,7 +59479,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59491,23 +59491,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59527,7 +59527,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59539,23 +59539,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>弗-乌-特-乌-尔-诶</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>future</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -59575,7 +59575,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59587,23 +59587,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -59623,7 +59623,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59635,23 +59635,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -59671,7 +59671,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59683,23 +59683,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -59719,103 +59719,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>普-伊-恩-克</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>struggle</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>struggle：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>斯-特-尔-乌-格-格-勒-诶</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>struggle</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>一句话：struggle：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -59076,7 +59076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59295,23 +59295,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>better：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>布-诶-特-特-诶-尔</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>布-勒-克</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/blak/</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>black</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -59326,12 +59330,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>blackball / blacklist / blacken</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>一句话：better：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
         </is>
       </c>
     </row>
@@ -59343,27 +59347,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>布-勒-克</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>/blak/</t>
-        </is>
-      </c>
+          <t>德-诶-勒-诶-特-诶</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -59378,12 +59378,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>blackball / blacklist / blacken</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59395,23 +59395,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>德-诶-勒</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59431,7 +59431,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：del：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59443,23 +59443,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59479,7 +59479,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59491,23 +59491,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59527,7 +59527,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59539,23 +59539,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>future：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>弗-乌-特-乌-尔-诶</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -59574,150 +59574,6 @@
         </is>
       </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>一句话：future：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>idemmode</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>idemmode</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>伊-斯</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>普-伊-恩-克</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -59076,7 +59076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59295,27 +59295,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>布-勒-克</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>/blak/</t>
-        </is>
-      </c>
+          <t>德-诶-勒-诶-特-诶</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -59330,12 +59326,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>blackball / blacklist / blacken</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>一句话：（有时大写）非洲人、原住民或毛利人后裔；皮肤黝黑的人。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59347,23 +59343,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -59383,7 +59379,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59395,23 +59391,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59431,7 +59427,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59443,23 +59439,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59479,7 +59475,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59491,23 +59487,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>伊-斯</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>/pɪŋk/</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59527,55 +59527,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>社区投稿</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pink：技术面试常见术语，建议结合项目场景理解。</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>普-伊-恩-克</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>一句话：pink：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J547"/>
+  <dimension ref="A1:J548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29736,6 +29736,58 @@
       <c r="J547" t="inlineStr">
         <is>
           <t>堆很大又要毫秒级停顿，ZGC 是候选。</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>社区·深度学习 · AI / 其他</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>checkpointer</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>checkpointer：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>克-赫-伊-克-克-普-欧-因特</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>/tʃekpɒɪntə/</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>/tʃekpɒɪntə/</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>AI / 其他</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>常问</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>能说明 checkpointer 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59076,7 +59128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59290,38 +59342,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·深度学习 · AI / 其他</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>checkpointer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>checkpointer：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>克-赫-伊-克-克-普-欧-因特</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/tʃekpɒɪntə/</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>/tʃekpɒɪntə/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>AI / 其他</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>了解</t>
+          <t>常问</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -59331,7 +59387,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 checkpointer 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59343,23 +59399,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -59379,7 +59435,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59391,23 +59447,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59427,7 +59483,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59439,23 +59495,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59475,7 +59531,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59487,45 +59543,93 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>伊-斯</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>普-伊-恩-克</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>/pɪŋk/</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J548"/>
+  <dimension ref="A1:J549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29788,6 +29788,58 @@
       <c r="J548" t="inlineStr">
         <is>
           <t>能说明 checkpointer 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>example：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>伊-克斯-阿-姆-普-勒-伊</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>/eksæmpəl/</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>/eksæmpəl/</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>能说明 example 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59128,7 +59180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59442,28 +59494,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>example</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>example：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>弗-尔</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>伊-克斯-阿-姆-普-勒-伊</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>/eksæmpəl/</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>/eksæmpəl/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59483,7 +59539,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 example 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59495,23 +59551,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59531,7 +59587,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59543,23 +59599,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59579,7 +59635,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59591,45 +59647,93 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>伊-斯</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>普-伊-恩-克</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>/pɪŋk/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J549"/>
+  <dimension ref="A1:J550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29840,6 +29840,58 @@
       <c r="J549" t="inlineStr">
         <is>
           <t>能说明 example 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>idepment</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>伊-德-伊-普-门特</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>/ɪdepmənt/</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>/ɪdepmənt/</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59180,7 +59232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59642,28 +59694,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idepment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>伊-斯</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>伊-德-伊-普-门特</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>/ɪdepmənt/</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>/ɪdepmənt/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -59683,7 +59739,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59695,45 +59751,93 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>伊-斯</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>普-伊-恩-克</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>/pɪŋk/</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>了解</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -59232,7 +59232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59840,6 +59840,58 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>社区·基础 · AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>提示词，引导模型输出</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>普-罗姆普特</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>/prɒmpt/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>/prɒmpt/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>System / Few-shot</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>引导模型输出的指令和上下文。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="10980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI分类-目录" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI分类-全部词汇" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python-FastAPI" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM-RAG-LangChain" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer-OpenCV" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docker-K8s" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI工具开发" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Java后端" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="架构通用" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="全部汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="社区添加单词" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="网页原文" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Java常用单词" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Python常用单词" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FastAPI常用单词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LangChain常用单词" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Python补充" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FastAPI补充" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LangChain与RAG补充" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Transformer补充" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="OpenCV补充" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AI编程工具补充" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Java后端补充" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="说明" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="AI分类-目录" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="AI分类-全部词汇" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Python-FastAPI" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="LLM-RAG-LangChain" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Transformer-OpenCV" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Docker-K8s" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="AI工具开发" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Java后端" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="架构通用" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -37362,7 +37362,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -37615,7 +37614,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
         <is>
@@ -38429,7 +38427,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
@@ -59309,7 +59306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59392,7 +59389,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/æd/</t>
+          <t>add</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -59437,10 +59434,14 @@
           <t>阿-德-姆-伊-恩-欧-普-伊-恩</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>/ædmɪnɒpen/</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>adminopen</t>
+          <t>/ædmɪnɒpen/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -59487,12 +59488,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>/ˈæp(ə)l/</t>
+          <t>/ˈæp.əl/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/ˈæp(ə)l/</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -59596,7 +59597,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/dɪˈliːt/</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -59633,22 +59634,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>example：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>伊-克斯-阿-姆-普-勒-伊</t>
+          <t>伊-格-兹-阿-姆-普-勒</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>英 /ɪɡˈzɑːmp(ə)l/  美 /ɪɡˈzæmp(ə)l/</t>
+          <t>/ɪɡˈzɑːmpl̩/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>英 /ɪɡˈzɑːmp(ə)l/  美 /ɪɡˈzæmp(ə)l/</t>
+          <t>/ɪɡˈzɑːmpl̩/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59668,7 +59669,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>能说明 example 的含义，并举例它在项目中的用法。</t>
+          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
         </is>
       </c>
     </row>
@@ -59700,7 +59701,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>英 /fɔː(r); fə(r)/  美 /fɔːr; fər/</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59745,6 +59746,7 @@
           <t>伊-德-诶-姆-姆-德-诶</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>idemmode</t>
@@ -59851,7 +59853,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/ɪz/</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -59903,7 +59905,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/pɪŋk/</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -59924,6 +59926,58 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>社区·基础 · AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>提示词，引导模型输出</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>普-罗姆普特</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>/prɒmpt/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>/prɒmpt/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>必问</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>System / Few-shot</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>引导模型输出的指令和上下文。</t>
         </is>
       </c>
     </row>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J550"/>
+  <dimension ref="A1:J549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29802,42 +29802,42 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>社区·深度学习 · AI / 其他</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>checkpointer</t>
+          <t>example</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>checkpointer：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>example：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>克-赫-伊-克-克-普-欧-因特</t>
+          <t>伊-克斯-阿-姆-普-勒-伊</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>/tʃekpɒɪntə/</t>
+          <t>英 /ɪɡˈzɑːmp(ə)l/  美 /ɪɡˈzæmp(ə)l/</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>/tʃekpɒɪntə/</t>
+          <t>英 /ɪɡˈzɑːmp(ə)l/  美 /ɪɡˈzæmp(ə)l/</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>AI / 其他</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>常问</t>
+          <t>了解</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -29847,7 +29847,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>能说明 checkpointer 的含义，并举例它在项目中的用法。</t>
+          <t>能说明 example 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -29859,27 +29859,27 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>idepment</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>example：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>伊-克斯-阿-姆-普-勒-伊</t>
+          <t>伊-德-伊-普-门特</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>英 /ɪɡˈzɑːmp(ə)l/  美 /ɪɡˈzæmp(ə)l/</t>
+          <t>/ɪdepmənt/</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>英 /ɪɡˈzɑːmp(ə)l/  美 /ɪɡˈzæmp(ə)l/</t>
+          <t>/ɪdepmənt/</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -29898,58 +29898,6 @@
         </is>
       </c>
       <c r="J549" t="inlineStr">
-        <is>
-          <t>能说明 example 的含义，并举例它在项目中的用法。</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>社区·未分类</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>idepment</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>伊-德-伊-普-门特</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>/ɪdepmənt/</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>/ɪdepmənt/</t>
-        </is>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>了解</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J550" t="inlineStr">
         <is>
           <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
         </is>
@@ -59306,7 +59254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59520,42 +59468,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>社区·深度学习 · AI / 其他</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>checkpointer</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>checkpointer：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>克-赫-伊-克-克-普-欧-因特</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>/tʃekpɒɪntə/</t>
+          <t>/dɪˈliːt/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/tʃekpɒɪntə/</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AI / 其他</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>常问</t>
+          <t>了解</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -59565,39 +59513,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>能说明 checkpointer 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>example</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>伊-格-兹-阿-姆-普-勒</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>/dɪˈliːt/</t>
+          <t>/ɪɡˈzɑːmpl̩/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>/ɪɡˈzɑːmpl̩/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -59617,39 +59565,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>伊-格-兹-阿-姆-普-勒</t>
+          <t>弗-尔</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>/ɪɡˈzɑːmpl̩/</t>
+          <t>英 /fɔː(r); fə(r)/  美 /fɔːr; fər/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/ɪɡˈzɑːmpl̩/</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59669,7 +59617,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59681,27 +59629,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>弗-尔</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>英 /fɔː(r); fə(r)/  美 /fɔːr; fər/</t>
-        </is>
-      </c>
+          <t>伊-德-诶-姆-姆-德-诶</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59721,35 +59665,39 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>idepment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>伊-德-伊-普-门特</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>/ɪdepmənt/</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>/ɪdepmənt/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59769,39 +59717,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>idepment</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>伊-德-伊-普-门特</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>/ɪdepmənt/</t>
+          <t>/ɪz/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/ɪdepmənt/</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -59821,7 +59769,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
@@ -59833,27 +59781,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>普-伊-恩-克</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>/ɪz/</t>
+          <t>/pɪŋk/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -59873,109 +59821,57 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·基础 · AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>prompt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>常见的小鱼， Phoxinus phoxinus。</t>
+          <t>提示词，引导模型输出</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>普-罗姆普特</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>/pɪŋk/</t>
+          <t>/prɒmpt/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>/prɒmpt/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>了解</t>
+          <t>必问</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>System / Few-shot</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
-        <is>
-          <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>社区·基础 · AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>prompt</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>提示词，引导模型输出</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>普-罗姆普特</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>/prɒmpt/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>/prɒmpt/</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>必问</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>System / Few-shot</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>引导模型输出的指令和上下文。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -59254,7 +59254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59468,37 +59468,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·JavaScript常用单词</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>debounce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>防抖函数</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>德-诶-勒-诶-特-诶</t>
+          <t>迪邦斯</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>/dɪˈliːt/</t>
+          <t>/dibauns/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>/dibauns/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -59508,44 +59508,44 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Debounce / Throttle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>防抖函数。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
+          <t>delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>伊-格-兹-阿-姆-普-勒</t>
+          <t>德-诶-勒-诶-特-诶</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>/ɪɡˈzɑːmpl̩/</t>
+          <t>/dɪˈliːt/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/ɪɡˈzɑːmpl̩/</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -59565,39 +59565,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
+          <t>一句话：delete：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>example</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>弗-尔</t>
+          <t>伊-格-兹-阿-姆-普-勒</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>英 /fɔː(r); fə(r)/  美 /fɔːr; fər/</t>
+          <t>/ɪɡˈzɑːmpl̩/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>for</t>
+          <t>/ɪɡˈzɑːmpl̩/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -59617,7 +59617,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>平行或非常相似的案例，特别是作为先例或模型时。</t>
         </is>
       </c>
     </row>
@@ -59629,23 +59629,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>伊-德-诶-姆-姆-德-诶</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>弗-尔</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>英 /fɔː(r); fə(r)/  美 /fɔːr; fər/</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>idemmode</t>
+          <t>for</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -59665,39 +59669,35 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>一句话：for：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>社区·未分类</t>
+          <t>社区投稿</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>idepment</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
+          <t>idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>伊-德-伊-普-门特</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>/ɪdepmənt/</t>
-        </is>
-      </c>
+          <t>伊-德-诶-姆-姆-德-诶</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/ɪdepmənt/</t>
+          <t>idemmode</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -59717,39 +59717,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
+          <t>一句话：idemmode：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>社区投稿</t>
+          <t>社区·未分类</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>idepment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>idepment：面试中需能解释其含义，并结合项目说明使用场景。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>伊-斯</t>
+          <t>伊-德-伊-普-门特</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>/ɪz/</t>
+          <t>/ɪdepmənt/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>/ɪdepmənt/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -59769,7 +59769,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
+          <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59781,27 +59781,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>常见的小鱼， Phoxinus phoxinus。</t>
+          <t>IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>普-伊-恩-克</t>
+          <t>伊-斯</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>/pɪŋk/</t>
+          <t>/ɪz/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -59821,57 +59821,109 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
+          <t>一句话：IS：技术面试常见术语，建议结合项目场景理解。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>社区投稿</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>常见的小鱼， Phoxinus phoxinus。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>普-伊-恩-克</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>/pɪŋk/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>一句话：常见的小鱼， Phoxinus phoxinus。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>社区·基础 · AI</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>prompt</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>提示词，引导模型输出</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>普-罗姆普特</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>/prɒmpt/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>/prɒmpt/</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>必问</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>System / Few-shot</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>引导模型输出的指令和上下文。</t>
         </is>

--- a/docs/interview-vocab.xlsx
+++ b/docs/interview-vocab.xlsx
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J549"/>
+  <dimension ref="A1:J550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29900,6 +29900,58 @@
       <c r="J549" t="inlineStr">
         <is>
           <t>能说明 idepment 的含义，并举例它在项目中的用法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Reconciliation：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>尔-诶-克-奥-恩-克-伊-勒-伊-阿-什-呃-恩</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>/rekɒnkɪlɪæʃən/</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>/rekɒnkɪlɪæʃən/</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>能说明 Reconciliation 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
@@ -59254,7 +59306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59926,6 +59978,58 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>引导模型输出的指令和上下文。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>社区·未分类</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Reconciliation：面试中需能解释其含义，并结合项目说明使用场景。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>尔-诶-克-奥-恩-克-伊-勒-伊-阿-什-呃-恩</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>/rekɒnkɪlɪæʃən/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>/rekɒnkɪlɪæʃən/</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>能说明 Reconciliation 的含义，并举例它在项目中的用法。</t>
         </is>
       </c>
     </row>
